--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609323</v>
+        <v>122609367</v>
       </c>
       <c r="B2" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556565</v>
+        <v>556579</v>
       </c>
       <c r="R2" t="n">
-        <v>7073614</v>
+        <v>7073612</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609410</v>
+        <v>122609485</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556627</v>
+        <v>556728</v>
       </c>
       <c r="R4" t="n">
-        <v>7073634</v>
+        <v>7073530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1128,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609510</v>
+        <v>122609428</v>
       </c>
       <c r="B6" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1164,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556718</v>
+        <v>556600</v>
       </c>
       <c r="R6" t="n">
-        <v>7073524</v>
+        <v>7073582</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1248,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609548</v>
+        <v>122609342</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1276,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556651</v>
+        <v>556567</v>
       </c>
       <c r="R7" t="n">
-        <v>7073522</v>
+        <v>7073613</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1464,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609392</v>
+        <v>122609510</v>
       </c>
       <c r="B9" t="n">
-        <v>90835</v>
+        <v>79737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1505,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556589</v>
+        <v>556718</v>
       </c>
       <c r="R9" t="n">
-        <v>7073595</v>
+        <v>7073524</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,22 +1589,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609428</v>
+        <v>122609323</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1617,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556600</v>
+        <v>556565</v>
       </c>
       <c r="R10" t="n">
-        <v>7073582</v>
+        <v>7073614</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,22 +1701,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122609342</v>
+        <v>122609410</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,39 +1729,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556567</v>
+        <v>556627</v>
       </c>
       <c r="R11" t="n">
-        <v>7073613</v>
+        <v>7073634</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,22 +1813,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609485</v>
+        <v>122609392</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>90835</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,39 +1841,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556728</v>
+        <v>556589</v>
       </c>
       <c r="R12" t="n">
-        <v>7073530</v>
+        <v>7073595</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,12 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,22 +1925,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609367</v>
+        <v>122609548</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,39 +1953,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556579</v>
+        <v>556651</v>
       </c>
       <c r="R13" t="n">
-        <v>7073612</v>
+        <v>7073522</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,12 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,12 +2037,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609367</v>
+        <v>122609428</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556579</v>
+        <v>556600</v>
       </c>
       <c r="R2" t="n">
-        <v>7073612</v>
+        <v>7073582</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609485</v>
+        <v>122609510</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556728</v>
+        <v>556718</v>
       </c>
       <c r="R4" t="n">
-        <v>7073530</v>
+        <v>7073524</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609722</v>
+        <v>122609410</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556563</v>
+        <v>556627</v>
       </c>
       <c r="R5" t="n">
-        <v>7073642</v>
+        <v>7073634</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609428</v>
+        <v>122609485</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,34 +1139,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556600</v>
+        <v>556728</v>
       </c>
       <c r="R6" t="n">
-        <v>7073582</v>
+        <v>7073530</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609342</v>
+        <v>122609367</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,16 +1261,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1305,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556567</v>
+        <v>556579</v>
       </c>
       <c r="R7" t="n">
-        <v>7073613</v>
+        <v>7073612</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1335,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609394</v>
+        <v>122609323</v>
       </c>
       <c r="B8" t="n">
-        <v>90857</v>
+        <v>79737</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556621</v>
+        <v>556565</v>
       </c>
       <c r="R8" t="n">
-        <v>7073625</v>
+        <v>7073614</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609510</v>
+        <v>122609394</v>
       </c>
       <c r="B9" t="n">
-        <v>79737</v>
+        <v>90851</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556718</v>
+        <v>556621</v>
       </c>
       <c r="R9" t="n">
-        <v>7073524</v>
+        <v>7073625</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609323</v>
+        <v>122609392</v>
       </c>
       <c r="B10" t="n">
-        <v>79737</v>
+        <v>90829</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556565</v>
+        <v>556589</v>
       </c>
       <c r="R10" t="n">
-        <v>7073614</v>
+        <v>7073595</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,19 +1691,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122609410</v>
+        <v>122609548</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1753,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556627</v>
+        <v>556651</v>
       </c>
       <c r="R11" t="n">
-        <v>7073634</v>
+        <v>7073522</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,22 +1803,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609392</v>
+        <v>122609722</v>
       </c>
       <c r="B12" t="n">
-        <v>90835</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,34 +1831,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556589</v>
+        <v>556563</v>
       </c>
       <c r="R12" t="n">
-        <v>7073595</v>
+        <v>7073642</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,22 +1920,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609548</v>
+        <v>122609342</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,34 +1948,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556651</v>
+        <v>556567</v>
       </c>
       <c r="R13" t="n">
-        <v>7073522</v>
+        <v>7073613</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609428</v>
+        <v>122609485</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556600</v>
+        <v>556728</v>
       </c>
       <c r="R2" t="n">
-        <v>7073582</v>
+        <v>7073530</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609450</v>
+        <v>122609722</v>
       </c>
       <c r="B3" t="n">
-        <v>79737</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +813,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556681</v>
+        <v>556563</v>
       </c>
       <c r="R3" t="n">
-        <v>7073593</v>
+        <v>7073642</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609510</v>
+        <v>122609367</v>
       </c>
       <c r="B4" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +930,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556718</v>
+        <v>556579</v>
       </c>
       <c r="R4" t="n">
-        <v>7073524</v>
+        <v>7073612</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +1004,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609410</v>
+        <v>122609392</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>90829</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1052,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556627</v>
+        <v>556589</v>
       </c>
       <c r="R5" t="n">
-        <v>7073634</v>
+        <v>7073595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1136,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609485</v>
+        <v>122609510</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,39 +1164,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556728</v>
+        <v>556718</v>
       </c>
       <c r="R6" t="n">
-        <v>7073530</v>
+        <v>7073524</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609367</v>
+        <v>122609323</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556579</v>
+        <v>556565</v>
       </c>
       <c r="R7" t="n">
-        <v>7073612</v>
+        <v>7073614</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,12 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609323</v>
+        <v>122609428</v>
       </c>
       <c r="B8" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556565</v>
+        <v>556600</v>
       </c>
       <c r="R8" t="n">
-        <v>7073614</v>
+        <v>7073582</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1472,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609394</v>
+        <v>122609410</v>
       </c>
       <c r="B9" t="n">
-        <v>90851</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1500,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556621</v>
+        <v>556627</v>
       </c>
       <c r="R9" t="n">
-        <v>7073625</v>
+        <v>7073634</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609392</v>
+        <v>122609342</v>
       </c>
       <c r="B10" t="n">
-        <v>90829</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,34 +1612,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556589</v>
+        <v>556567</v>
       </c>
       <c r="R10" t="n">
-        <v>7073595</v>
+        <v>7073613</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122609548</v>
+        <v>122609394</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>90851</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,21 +1729,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556651</v>
+        <v>556621</v>
       </c>
       <c r="R11" t="n">
-        <v>7073522</v>
+        <v>7073625</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,22 +1813,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609722</v>
+        <v>122609450</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>79737</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,42 +1841,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556563</v>
+        <v>556681</v>
       </c>
       <c r="R12" t="n">
-        <v>7073642</v>
+        <v>7073593</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609342</v>
+        <v>122609548</v>
       </c>
       <c r="B13" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,39 +1953,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556567</v>
+        <v>556651</v>
       </c>
       <c r="R13" t="n">
-        <v>7073613</v>
+        <v>7073522</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609485</v>
+        <v>122609548</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556728</v>
+        <v>556651</v>
       </c>
       <c r="R2" t="n">
-        <v>7073530</v>
+        <v>7073522</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609722</v>
+        <v>122609367</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556563</v>
+        <v>556579</v>
       </c>
       <c r="R3" t="n">
-        <v>7073642</v>
+        <v>7073612</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609367</v>
+        <v>122609428</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556579</v>
+        <v>556600</v>
       </c>
       <c r="R4" t="n">
-        <v>7073612</v>
+        <v>7073582</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,12 +1009,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1039,7 +1024,7 @@
         <v>122609392</v>
       </c>
       <c r="B5" t="n">
-        <v>90829</v>
+        <v>90830</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1148,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609510</v>
+        <v>122609394</v>
       </c>
       <c r="B6" t="n">
-        <v>79737</v>
+        <v>90852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556718</v>
+        <v>556621</v>
       </c>
       <c r="R6" t="n">
-        <v>7073524</v>
+        <v>7073625</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609323</v>
+        <v>122609485</v>
       </c>
       <c r="B7" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,34 +1261,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556565</v>
+        <v>556728</v>
       </c>
       <c r="R7" t="n">
-        <v>7073614</v>
+        <v>7073530</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1335,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609428</v>
+        <v>122609450</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,13 +1407,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556600</v>
+        <v>556681</v>
       </c>
       <c r="R8" t="n">
-        <v>7073582</v>
+        <v>7073593</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609410</v>
+        <v>122609342</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,34 +1495,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556627</v>
+        <v>556567</v>
       </c>
       <c r="R9" t="n">
-        <v>7073634</v>
+        <v>7073613</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,22 +1584,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609342</v>
+        <v>122609510</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>79738</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,39 +1612,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556567</v>
+        <v>556718</v>
       </c>
       <c r="R10" t="n">
-        <v>7073613</v>
+        <v>7073524</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,22 +1696,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122609394</v>
+        <v>122609410</v>
       </c>
       <c r="B11" t="n">
-        <v>90851</v>
+        <v>78657</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,21 +1724,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556621</v>
+        <v>556627</v>
       </c>
       <c r="R11" t="n">
-        <v>7073625</v>
+        <v>7073634</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609450</v>
+        <v>122609722</v>
       </c>
       <c r="B12" t="n">
-        <v>79737</v>
+        <v>57400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,37 +1836,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556681</v>
+        <v>556563</v>
       </c>
       <c r="R12" t="n">
-        <v>7073593</v>
+        <v>7073642</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609548</v>
+        <v>122609323</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,21 +1953,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556651</v>
+        <v>556565</v>
       </c>
       <c r="R13" t="n">
-        <v>7073522</v>
+        <v>7073614</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,12 +2037,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609548</v>
+        <v>122609394</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
+        <v>90855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556651</v>
+        <v>556621</v>
       </c>
       <c r="R2" t="n">
-        <v>7073522</v>
+        <v>7073625</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609367</v>
+        <v>122609510</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556579</v>
+        <v>556718</v>
       </c>
       <c r="R3" t="n">
-        <v>7073612</v>
+        <v>7073524</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609428</v>
+        <v>122609367</v>
       </c>
       <c r="B4" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556600</v>
+        <v>556579</v>
       </c>
       <c r="R4" t="n">
-        <v>7073582</v>
+        <v>7073612</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609392</v>
+        <v>122609342</v>
       </c>
       <c r="B5" t="n">
-        <v>90830</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556589</v>
+        <v>556567</v>
       </c>
       <c r="R5" t="n">
-        <v>7073595</v>
+        <v>7073613</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609394</v>
+        <v>122609485</v>
       </c>
       <c r="B6" t="n">
-        <v>90852</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1154,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556621</v>
+        <v>556728</v>
       </c>
       <c r="R6" t="n">
-        <v>7073625</v>
+        <v>7073530</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609485</v>
+        <v>122609548</v>
       </c>
       <c r="B7" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556728</v>
+        <v>556651</v>
       </c>
       <c r="R7" t="n">
-        <v>7073530</v>
+        <v>7073522</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,12 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,22 +1360,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609450</v>
+        <v>122609428</v>
       </c>
       <c r="B8" t="n">
-        <v>79738</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,13 +1412,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556681</v>
+        <v>556600</v>
       </c>
       <c r="R8" t="n">
-        <v>7073593</v>
+        <v>7073582</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1472,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609342</v>
+        <v>122609410</v>
       </c>
       <c r="B9" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,39 +1500,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556567</v>
+        <v>556627</v>
       </c>
       <c r="R9" t="n">
-        <v>7073613</v>
+        <v>7073634</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,22 +1584,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609510</v>
+        <v>122609323</v>
       </c>
       <c r="B10" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556718</v>
+        <v>556565</v>
       </c>
       <c r="R10" t="n">
-        <v>7073524</v>
+        <v>7073614</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122609410</v>
+        <v>122609722</v>
       </c>
       <c r="B11" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,34 +1724,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556627</v>
+        <v>556563</v>
       </c>
       <c r="R11" t="n">
-        <v>7073634</v>
+        <v>7073642</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609722</v>
+        <v>122609392</v>
       </c>
       <c r="B12" t="n">
-        <v>57400</v>
+        <v>90833</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,39 +1841,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556563</v>
+        <v>556589</v>
       </c>
       <c r="R12" t="n">
-        <v>7073642</v>
+        <v>7073595</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,22 +1925,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609323</v>
+        <v>122609450</v>
       </c>
       <c r="B13" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,13 +1977,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556565</v>
+        <v>556681</v>
       </c>
       <c r="R13" t="n">
-        <v>7073614</v>
+        <v>7073593</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609394</v>
+        <v>122609428</v>
       </c>
       <c r="B2" t="n">
-        <v>90855</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556621</v>
+        <v>556600</v>
       </c>
       <c r="R2" t="n">
-        <v>7073625</v>
+        <v>7073582</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609510</v>
+        <v>122609323</v>
       </c>
       <c r="B3" t="n">
         <v>79741</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556718</v>
+        <v>556565</v>
       </c>
       <c r="R3" t="n">
-        <v>7073524</v>
+        <v>7073614</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609367</v>
+        <v>122609410</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556579</v>
+        <v>556627</v>
       </c>
       <c r="R4" t="n">
-        <v>7073612</v>
+        <v>7073634</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609342</v>
+        <v>122609722</v>
       </c>
       <c r="B5" t="n">
         <v>57400</v>
@@ -1057,7 +1047,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556567</v>
+        <v>556563</v>
       </c>
       <c r="R5" t="n">
-        <v>7073613</v>
+        <v>7073642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,12 +1116,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1260,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609548</v>
+        <v>122609392</v>
       </c>
       <c r="B7" t="n">
-        <v>78660</v>
+        <v>90833</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556651</v>
+        <v>556589</v>
       </c>
       <c r="R7" t="n">
-        <v>7073522</v>
+        <v>7073595</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609428</v>
+        <v>122609450</v>
       </c>
       <c r="B8" t="n">
-        <v>78660</v>
+        <v>79741</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,13 +1402,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556600</v>
+        <v>556681</v>
       </c>
       <c r="R8" t="n">
-        <v>7073582</v>
+        <v>7073593</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,22 +1462,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609410</v>
+        <v>122609342</v>
       </c>
       <c r="B9" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,34 +1490,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556627</v>
+        <v>556567</v>
       </c>
       <c r="R9" t="n">
-        <v>7073634</v>
+        <v>7073613</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,22 +1579,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609323</v>
+        <v>122609367</v>
       </c>
       <c r="B10" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,34 +1607,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556565</v>
+        <v>556579</v>
       </c>
       <c r="R10" t="n">
-        <v>7073614</v>
+        <v>7073612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1681,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122609722</v>
+        <v>122609510</v>
       </c>
       <c r="B11" t="n">
-        <v>57400</v>
+        <v>79741</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,39 +1729,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556563</v>
+        <v>556718</v>
       </c>
       <c r="R11" t="n">
-        <v>7073642</v>
+        <v>7073524</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609392</v>
+        <v>122609394</v>
       </c>
       <c r="B12" t="n">
-        <v>90833</v>
+        <v>90855</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556589</v>
+        <v>556621</v>
       </c>
       <c r="R12" t="n">
-        <v>7073595</v>
+        <v>7073625</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,22 +1925,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609450</v>
+        <v>122609548</v>
       </c>
       <c r="B13" t="n">
-        <v>79741</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,21 +1953,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1977,13 +1977,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556681</v>
+        <v>556651</v>
       </c>
       <c r="R13" t="n">
-        <v>7073593</v>
+        <v>7073522</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,12 +2037,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2626,6 +2626,1369 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122854281</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56680</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hopslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>556676</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7073548</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122854275</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hopslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>556654</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7073470</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122854286</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90958</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hopslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>556650</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7073472</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122854276</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56078</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hopslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>556646</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7073479</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122854279</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56680</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hopslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>556629</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7073587</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122854285</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90958</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hopslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>556623</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7073654</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122854282</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90958</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hopslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>556672</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7073600</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122854280</v>
+      </c>
+      <c r="B26" t="n">
+        <v>56680</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hopslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>556618</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7073638</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122854278</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79879</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hopslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>556670</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7073582</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122854277</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79843</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hopslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>556696</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7073607</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122854288</v>
+      </c>
+      <c r="B29" t="n">
+        <v>82549</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hopslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>556613</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7073551</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122854287</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90958</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hopslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>556626</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7073546</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122854284</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90958</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hopslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>556746</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7073511</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -2052,7 +2052,7 @@
         <v>122805086</v>
       </c>
       <c r="B14" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122806389</v>
+        <v>122802647</v>
       </c>
       <c r="B17" t="n">
-        <v>79843</v>
+        <v>57631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,34 +2411,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556570</v>
+        <v>556662</v>
       </c>
       <c r="R17" t="n">
-        <v>7073597</v>
+        <v>7073528</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2480,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122802647</v>
+        <v>122806389</v>
       </c>
       <c r="B18" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,43 +2532,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556662</v>
+        <v>556570</v>
       </c>
       <c r="R18" t="n">
-        <v>7073528</v>
+        <v>7073597</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,7 +2628,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122854281</v>
+        <v>122854279</v>
       </c>
       <c r="B19" t="n">
         <v>56680</v>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556676</v>
+        <v>556629</v>
       </c>
       <c r="R19" t="n">
-        <v>7073548</v>
+        <v>7073587</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122854286</v>
+        <v>122854278</v>
       </c>
       <c r="B21" t="n">
-        <v>90958</v>
+        <v>79883</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2857,25 +2857,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556650</v>
+        <v>556670</v>
       </c>
       <c r="R21" t="n">
-        <v>7073472</v>
+        <v>7073582</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122854276</v>
+        <v>122854277</v>
       </c>
       <c r="B22" t="n">
-        <v>56078</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2963,42 +2963,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556646</v>
+        <v>556696</v>
       </c>
       <c r="R22" t="n">
-        <v>7073479</v>
+        <v>7073607</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3057,10 +3049,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122854279</v>
+        <v>122854287</v>
       </c>
       <c r="B23" t="n">
-        <v>56680</v>
+        <v>90962</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3073,42 +3065,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556629</v>
+        <v>556626</v>
       </c>
       <c r="R23" t="n">
-        <v>7073587</v>
+        <v>7073546</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3170,7 +3154,7 @@
         <v>122854285</v>
       </c>
       <c r="B24" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3269,10 +3253,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122854282</v>
+        <v>122854286</v>
       </c>
       <c r="B25" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3309,10 +3293,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556672</v>
+        <v>556650</v>
       </c>
       <c r="R25" t="n">
-        <v>7073600</v>
+        <v>7073472</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3371,10 +3355,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122854280</v>
+        <v>122854282</v>
       </c>
       <c r="B26" t="n">
-        <v>56680</v>
+        <v>90962</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3387,42 +3371,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556618</v>
+        <v>556672</v>
       </c>
       <c r="R26" t="n">
-        <v>7073638</v>
+        <v>7073600</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3481,10 +3457,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122854278</v>
+        <v>122854281</v>
       </c>
       <c r="B27" t="n">
-        <v>79879</v>
+        <v>56680</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3493,38 +3469,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556670</v>
+        <v>556676</v>
       </c>
       <c r="R27" t="n">
-        <v>7073582</v>
+        <v>7073548</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3583,10 +3567,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122854277</v>
+        <v>122854276</v>
       </c>
       <c r="B28" t="n">
-        <v>79843</v>
+        <v>56078</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3599,34 +3583,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556696</v>
+        <v>556646</v>
       </c>
       <c r="R28" t="n">
-        <v>7073607</v>
+        <v>7073479</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3688,7 +3680,7 @@
         <v>122854288</v>
       </c>
       <c r="B29" t="n">
-        <v>82549</v>
+        <v>82553</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3787,10 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122854287</v>
+        <v>122854280</v>
       </c>
       <c r="B30" t="n">
-        <v>90958</v>
+        <v>56680</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3803,34 +3795,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556626</v>
+        <v>556618</v>
       </c>
       <c r="R30" t="n">
-        <v>7073546</v>
+        <v>7073638</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3892,7 +3892,7 @@
         <v>122854284</v>
       </c>
       <c r="B31" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609510</v>
+        <v>122609392</v>
       </c>
       <c r="B2" t="n">
-        <v>79843</v>
+        <v>90940</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556718</v>
+        <v>556589</v>
       </c>
       <c r="R2" t="n">
-        <v>7073524</v>
+        <v>7073595</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609367</v>
+        <v>122609450</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556579</v>
+        <v>556681</v>
       </c>
       <c r="R3" t="n">
-        <v>7073612</v>
+        <v>7073593</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609485</v>
+        <v>122609394</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556728</v>
+        <v>556621</v>
       </c>
       <c r="R4" t="n">
-        <v>7073530</v>
+        <v>7073625</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609342</v>
+        <v>122609722</v>
       </c>
       <c r="B5" t="n">
         <v>57494</v>
@@ -1067,7 +1047,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556567</v>
+        <v>556563</v>
       </c>
       <c r="R5" t="n">
-        <v>7073613</v>
+        <v>7073642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609392</v>
+        <v>122609323</v>
       </c>
       <c r="B6" t="n">
-        <v>90936</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556589</v>
+        <v>556565</v>
       </c>
       <c r="R6" t="n">
-        <v>7073595</v>
+        <v>7073614</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609722</v>
+        <v>122609510</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,39 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556563</v>
+        <v>556718</v>
       </c>
       <c r="R7" t="n">
-        <v>7073642</v>
+        <v>7073524</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609548</v>
+        <v>122609428</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556651</v>
+        <v>556600</v>
       </c>
       <c r="R8" t="n">
-        <v>7073522</v>
+        <v>7073582</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609410</v>
+        <v>122609548</v>
       </c>
       <c r="B9" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556627</v>
+        <v>556651</v>
       </c>
       <c r="R9" t="n">
-        <v>7073634</v>
+        <v>7073522</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,22 +1564,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609323</v>
+        <v>122609367</v>
       </c>
       <c r="B10" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,34 +1592,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556565</v>
+        <v>556579</v>
       </c>
       <c r="R10" t="n">
-        <v>7073614</v>
+        <v>7073612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1666,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122609428</v>
+        <v>122609410</v>
       </c>
       <c r="B11" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556600</v>
+        <v>556627</v>
       </c>
       <c r="R11" t="n">
-        <v>7073582</v>
+        <v>7073634</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,22 +1798,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609450</v>
+        <v>122609342</v>
       </c>
       <c r="B12" t="n">
-        <v>79843</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,37 +1826,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556681</v>
+        <v>556567</v>
       </c>
       <c r="R12" t="n">
-        <v>7073593</v>
+        <v>7073613</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,22 +1915,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609394</v>
+        <v>122609485</v>
       </c>
       <c r="B13" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,34 +1943,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556621</v>
+        <v>556728</v>
       </c>
       <c r="R13" t="n">
-        <v>7073625</v>
+        <v>7073530</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2017,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609392</v>
+        <v>122609342</v>
       </c>
       <c r="B2" t="n">
-        <v>90940</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556589</v>
+        <v>556567</v>
       </c>
       <c r="R2" t="n">
-        <v>7073595</v>
+        <v>7073613</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609450</v>
+        <v>122609485</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +808,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556681</v>
+        <v>556728</v>
       </c>
       <c r="R3" t="n">
-        <v>7073593</v>
+        <v>7073530</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609394</v>
+        <v>122609548</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556621</v>
+        <v>556651</v>
       </c>
       <c r="R4" t="n">
-        <v>7073625</v>
+        <v>7073522</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609722</v>
+        <v>122609428</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556563</v>
+        <v>556600</v>
       </c>
       <c r="R5" t="n">
-        <v>7073642</v>
+        <v>7073582</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609323</v>
+        <v>122609394</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556565</v>
+        <v>556621</v>
       </c>
       <c r="R6" t="n">
-        <v>7073614</v>
+        <v>7073625</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609510</v>
+        <v>122609323</v>
       </c>
       <c r="B7" t="n">
         <v>79847</v>
@@ -1280,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556718</v>
+        <v>556565</v>
       </c>
       <c r="R7" t="n">
-        <v>7073524</v>
+        <v>7073614</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609428</v>
+        <v>122609722</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,34 +1378,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556600</v>
+        <v>556563</v>
       </c>
       <c r="R8" t="n">
-        <v>7073582</v>
+        <v>7073642</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609548</v>
+        <v>122609392</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>90940</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556651</v>
+        <v>556589</v>
       </c>
       <c r="R9" t="n">
-        <v>7073522</v>
+        <v>7073595</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609367</v>
+        <v>122609510</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,39 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556579</v>
+        <v>556718</v>
       </c>
       <c r="R10" t="n">
-        <v>7073612</v>
+        <v>7073524</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,12 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1810,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609342</v>
+        <v>122609367</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,16 +1831,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1855,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556567</v>
+        <v>556579</v>
       </c>
       <c r="R12" t="n">
-        <v>7073613</v>
+        <v>7073612</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1905,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,22 +1925,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609485</v>
+        <v>122609450</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,42 +1953,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556728</v>
+        <v>556681</v>
       </c>
       <c r="R13" t="n">
-        <v>7073530</v>
+        <v>7073593</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2007,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,12 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122805086</v>
+        <v>122802647</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,34 +2065,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556765</v>
+        <v>556662</v>
       </c>
       <c r="R14" t="n">
-        <v>7073489</v>
+        <v>7073528</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122802567</v>
+        <v>122802580</v>
       </c>
       <c r="B15" t="n">
-        <v>57494</v>
+        <v>56680</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,16 +2186,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2197,7 +2206,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2206,10 +2215,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556610</v>
+        <v>556617</v>
       </c>
       <c r="R15" t="n">
-        <v>7073643</v>
+        <v>7073617</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122802580</v>
+        <v>122805086</v>
       </c>
       <c r="B16" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,39 +2303,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556617</v>
+        <v>556765</v>
       </c>
       <c r="R16" t="n">
-        <v>7073617</v>
+        <v>7073489</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2358,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2368,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122802647</v>
+        <v>122806389</v>
       </c>
       <c r="B17" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,43 +2415,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556662</v>
+        <v>556570</v>
       </c>
       <c r="R17" t="n">
-        <v>7073528</v>
+        <v>7073597</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2484,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122806389</v>
+        <v>122802567</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,34 +2527,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556570</v>
+        <v>556610</v>
       </c>
       <c r="R18" t="n">
-        <v>7073597</v>
+        <v>7073643</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122854279</v>
+        <v>122854275</v>
       </c>
       <c r="B19" t="n">
-        <v>56680</v>
+        <v>57631</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,42 +2644,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556629</v>
+        <v>556654</v>
       </c>
       <c r="R19" t="n">
-        <v>7073587</v>
+        <v>7073470</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2738,10 +2735,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122854275</v>
+        <v>122854278</v>
       </c>
       <c r="B20" t="n">
-        <v>57631</v>
+        <v>79883</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,43 +2747,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556654</v>
+        <v>556670</v>
       </c>
       <c r="R20" t="n">
-        <v>7073470</v>
+        <v>7073582</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2845,10 +2837,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122854278</v>
+        <v>122854277</v>
       </c>
       <c r="B21" t="n">
-        <v>79883</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2857,25 +2849,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2885,10 +2877,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556670</v>
+        <v>556696</v>
       </c>
       <c r="R21" t="n">
-        <v>7073582</v>
+        <v>7073607</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2947,10 +2939,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122854277</v>
+        <v>122854285</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2963,21 +2955,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2987,10 +2979,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556696</v>
+        <v>556623</v>
       </c>
       <c r="R22" t="n">
-        <v>7073607</v>
+        <v>7073654</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3151,7 +3143,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122854285</v>
+        <v>122854286</v>
       </c>
       <c r="B24" t="n">
         <v>90962</v>
@@ -3191,10 +3183,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556623</v>
+        <v>556650</v>
       </c>
       <c r="R24" t="n">
-        <v>7073654</v>
+        <v>7073472</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3253,10 +3245,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122854286</v>
+        <v>122854288</v>
       </c>
       <c r="B25" t="n">
-        <v>90962</v>
+        <v>82553</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3269,21 +3261,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3293,10 +3285,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556650</v>
+        <v>556613</v>
       </c>
       <c r="R25" t="n">
-        <v>7073472</v>
+        <v>7073551</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3457,10 +3449,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122854281</v>
+        <v>122854284</v>
       </c>
       <c r="B27" t="n">
-        <v>56680</v>
+        <v>90962</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3473,42 +3465,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556676</v>
+        <v>556746</v>
       </c>
       <c r="R27" t="n">
-        <v>7073548</v>
+        <v>7073511</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3567,10 +3551,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122854276</v>
+        <v>122854279</v>
       </c>
       <c r="B28" t="n">
-        <v>56078</v>
+        <v>56680</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3583,21 +3567,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>206004</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3615,10 +3599,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556646</v>
+        <v>556629</v>
       </c>
       <c r="R28" t="n">
-        <v>7073479</v>
+        <v>7073587</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3677,10 +3661,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122854288</v>
+        <v>122854281</v>
       </c>
       <c r="B29" t="n">
-        <v>82553</v>
+        <v>56680</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3693,34 +3677,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556613</v>
+        <v>556676</v>
       </c>
       <c r="R29" t="n">
-        <v>7073551</v>
+        <v>7073548</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3889,10 +3881,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122854284</v>
+        <v>122854276</v>
       </c>
       <c r="B31" t="n">
-        <v>90962</v>
+        <v>56078</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3905,34 +3897,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>206004</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556746</v>
+        <v>556646</v>
       </c>
       <c r="R31" t="n">
-        <v>7073511</v>
+        <v>7073479</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609342</v>
+        <v>122609392</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>90940</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556567</v>
+        <v>556589</v>
       </c>
       <c r="R2" t="n">
-        <v>7073613</v>
+        <v>7073595</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609485</v>
+        <v>122609548</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556728</v>
+        <v>556651</v>
       </c>
       <c r="R3" t="n">
-        <v>7073530</v>
+        <v>7073522</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609548</v>
+        <v>122609367</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556651</v>
+        <v>556579</v>
       </c>
       <c r="R4" t="n">
-        <v>7073522</v>
+        <v>7073612</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609428</v>
+        <v>122609394</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556600</v>
+        <v>556621</v>
       </c>
       <c r="R5" t="n">
-        <v>7073582</v>
+        <v>7073625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609394</v>
+        <v>122609722</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556621</v>
+        <v>556563</v>
       </c>
       <c r="R6" t="n">
-        <v>7073625</v>
+        <v>7073642</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609323</v>
+        <v>122609428</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556565</v>
+        <v>556600</v>
       </c>
       <c r="R7" t="n">
-        <v>7073614</v>
+        <v>7073582</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,19 +1350,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609722</v>
+        <v>122609342</v>
       </c>
       <c r="B8" t="n">
         <v>57494</v>
@@ -1398,7 +1398,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556563</v>
+        <v>556567</v>
       </c>
       <c r="R8" t="n">
-        <v>7073642</v>
+        <v>7073613</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609392</v>
+        <v>122609510</v>
       </c>
       <c r="B9" t="n">
-        <v>90940</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556589</v>
+        <v>556718</v>
       </c>
       <c r="R9" t="n">
-        <v>7073595</v>
+        <v>7073524</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,19 +1579,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609510</v>
+        <v>122609323</v>
       </c>
       <c r="B10" t="n">
         <v>79847</v>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556718</v>
+        <v>556565</v>
       </c>
       <c r="R10" t="n">
-        <v>7073524</v>
+        <v>7073614</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1815,7 +1815,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609367</v>
+        <v>122609485</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1856,14 +1856,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556579</v>
+        <v>556728</v>
       </c>
       <c r="R12" t="n">
-        <v>7073612</v>
+        <v>7073530</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122802647</v>
+        <v>122802580</v>
       </c>
       <c r="B14" t="n">
-        <v>57631</v>
+        <v>56680</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,31 +2065,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2098,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556662</v>
+        <v>556617</v>
       </c>
       <c r="R14" t="n">
-        <v>7073528</v>
+        <v>7073617</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122802580</v>
+        <v>122805086</v>
       </c>
       <c r="B15" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,39 +2182,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556617</v>
+        <v>556765</v>
       </c>
       <c r="R15" t="n">
-        <v>7073617</v>
+        <v>7073489</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2250,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,7 +2278,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122805086</v>
+        <v>122806389</v>
       </c>
       <c r="B16" t="n">
         <v>79847</v>
@@ -2327,10 +2318,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556765</v>
+        <v>556570</v>
       </c>
       <c r="R16" t="n">
-        <v>7073489</v>
+        <v>7073597</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2353,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2363,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122806389</v>
+        <v>122802567</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,34 +2406,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556570</v>
+        <v>556610</v>
       </c>
       <c r="R17" t="n">
-        <v>7073597</v>
+        <v>7073643</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,7 +2470,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2480,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2507,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122802567</v>
+        <v>122802647</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,27 +2523,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556610</v>
+        <v>556662</v>
       </c>
       <c r="R18" t="n">
-        <v>7073643</v>
+        <v>7073528</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122854275</v>
+        <v>122854282</v>
       </c>
       <c r="B19" t="n">
-        <v>57631</v>
+        <v>90962</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,39 +2644,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556654</v>
+        <v>556672</v>
       </c>
       <c r="R19" t="n">
-        <v>7073470</v>
+        <v>7073600</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2735,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122854278</v>
+        <v>122854281</v>
       </c>
       <c r="B20" t="n">
-        <v>79883</v>
+        <v>56680</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2747,38 +2742,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556670</v>
+        <v>556676</v>
       </c>
       <c r="R20" t="n">
-        <v>7073582</v>
+        <v>7073548</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2837,10 +2840,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122854277</v>
+        <v>122854285</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2853,21 +2856,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2877,10 +2880,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556696</v>
+        <v>556623</v>
       </c>
       <c r="R21" t="n">
-        <v>7073607</v>
+        <v>7073654</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2939,10 +2942,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122854285</v>
+        <v>122854278</v>
       </c>
       <c r="B22" t="n">
-        <v>90962</v>
+        <v>79883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2951,25 +2954,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2979,10 +2982,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556623</v>
+        <v>556670</v>
       </c>
       <c r="R22" t="n">
-        <v>7073654</v>
+        <v>7073582</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3041,10 +3044,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122854287</v>
+        <v>122854279</v>
       </c>
       <c r="B23" t="n">
-        <v>90962</v>
+        <v>56680</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,34 +3060,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556626</v>
+        <v>556629</v>
       </c>
       <c r="R23" t="n">
-        <v>7073546</v>
+        <v>7073587</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3143,10 +3154,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122854286</v>
+        <v>122854288</v>
       </c>
       <c r="B24" t="n">
-        <v>90962</v>
+        <v>82553</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3159,21 +3170,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3183,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556650</v>
+        <v>556613</v>
       </c>
       <c r="R24" t="n">
-        <v>7073472</v>
+        <v>7073551</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3245,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122854288</v>
+        <v>122854287</v>
       </c>
       <c r="B25" t="n">
-        <v>82553</v>
+        <v>90962</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3261,21 +3272,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3285,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556613</v>
+        <v>556626</v>
       </c>
       <c r="R25" t="n">
-        <v>7073551</v>
+        <v>7073546</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3347,10 +3358,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122854282</v>
+        <v>122854280</v>
       </c>
       <c r="B26" t="n">
-        <v>90962</v>
+        <v>56680</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3363,34 +3374,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556672</v>
+        <v>556618</v>
       </c>
       <c r="R26" t="n">
-        <v>7073600</v>
+        <v>7073638</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3449,10 +3468,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122854284</v>
+        <v>122854277</v>
       </c>
       <c r="B27" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3465,21 +3484,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3489,10 +3508,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556746</v>
+        <v>556696</v>
       </c>
       <c r="R27" t="n">
-        <v>7073511</v>
+        <v>7073607</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3551,10 +3570,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122854279</v>
+        <v>122854286</v>
       </c>
       <c r="B28" t="n">
-        <v>56680</v>
+        <v>90962</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3567,42 +3586,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556629</v>
+        <v>556650</v>
       </c>
       <c r="R28" t="n">
-        <v>7073587</v>
+        <v>7073472</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3661,10 +3672,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122854281</v>
+        <v>122854284</v>
       </c>
       <c r="B29" t="n">
-        <v>56680</v>
+        <v>90962</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3677,42 +3688,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556676</v>
+        <v>556746</v>
       </c>
       <c r="R29" t="n">
-        <v>7073548</v>
+        <v>7073511</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3771,10 +3774,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122854280</v>
+        <v>122854275</v>
       </c>
       <c r="B30" t="n">
-        <v>56680</v>
+        <v>57631</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3787,42 +3790,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556618</v>
+        <v>556654</v>
       </c>
       <c r="R30" t="n">
-        <v>7073638</v>
+        <v>7073470</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122609410</v>
+        <v>122609485</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,34 +1719,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556627</v>
+        <v>556728</v>
       </c>
       <c r="R11" t="n">
-        <v>7073634</v>
+        <v>7073530</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609485</v>
+        <v>122609410</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,39 +1841,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556728</v>
+        <v>556627</v>
       </c>
       <c r="R12" t="n">
-        <v>7073530</v>
+        <v>7073634</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,12 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122802580</v>
+        <v>122805086</v>
       </c>
       <c r="B14" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,39 +2065,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556617</v>
+        <v>556765</v>
       </c>
       <c r="R14" t="n">
-        <v>7073617</v>
+        <v>7073489</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122805086</v>
+        <v>122802580</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,34 +2177,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556765</v>
+        <v>556617</v>
       </c>
       <c r="R15" t="n">
-        <v>7073489</v>
+        <v>7073617</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3358,10 +3358,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122854280</v>
+        <v>122854277</v>
       </c>
       <c r="B26" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3374,42 +3374,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556618</v>
+        <v>556696</v>
       </c>
       <c r="R26" t="n">
-        <v>7073638</v>
+        <v>7073607</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3468,10 +3460,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122854277</v>
+        <v>122854280</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3484,34 +3476,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556696</v>
+        <v>556618</v>
       </c>
       <c r="R27" t="n">
-        <v>7073607</v>
+        <v>7073638</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122805086</v>
+        <v>122802580</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,34 +2065,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556765</v>
+        <v>556617</v>
       </c>
       <c r="R14" t="n">
-        <v>7073489</v>
+        <v>7073617</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122802580</v>
+        <v>122805086</v>
       </c>
       <c r="B15" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,39 +2182,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556617</v>
+        <v>556765</v>
       </c>
       <c r="R15" t="n">
-        <v>7073617</v>
+        <v>7073489</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609392</v>
+        <v>122609323</v>
       </c>
       <c r="B2" t="n">
-        <v>90940</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556589</v>
+        <v>556565</v>
       </c>
       <c r="R2" t="n">
-        <v>7073595</v>
+        <v>7073614</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609548</v>
+        <v>122609722</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556651</v>
+        <v>556563</v>
       </c>
       <c r="R3" t="n">
-        <v>7073522</v>
+        <v>7073642</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609367</v>
+        <v>122609510</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556579</v>
+        <v>556718</v>
       </c>
       <c r="R4" t="n">
-        <v>7073612</v>
+        <v>7073524</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609394</v>
+        <v>122609342</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556621</v>
+        <v>556567</v>
       </c>
       <c r="R5" t="n">
-        <v>7073625</v>
+        <v>7073613</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609722</v>
+        <v>122609392</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>90940</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556563</v>
+        <v>556589</v>
       </c>
       <c r="R6" t="n">
-        <v>7073642</v>
+        <v>7073595</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1233,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1362,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609342</v>
+        <v>122609548</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,39 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556567</v>
+        <v>556651</v>
       </c>
       <c r="R8" t="n">
-        <v>7073613</v>
+        <v>7073522</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609510</v>
+        <v>122609450</v>
       </c>
       <c r="B9" t="n">
         <v>79847</v>
@@ -1519,13 +1509,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556718</v>
+        <v>556681</v>
       </c>
       <c r="R9" t="n">
-        <v>7073524</v>
+        <v>7073593</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609323</v>
+        <v>122609394</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1597,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556565</v>
+        <v>556621</v>
       </c>
       <c r="R10" t="n">
-        <v>7073614</v>
+        <v>7073625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122609485</v>
+        <v>122609410</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,39 +1709,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556728</v>
+        <v>556627</v>
       </c>
       <c r="R11" t="n">
-        <v>7073530</v>
+        <v>7073634</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,12 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609410</v>
+        <v>122609367</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,34 +1821,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556627</v>
+        <v>556579</v>
       </c>
       <c r="R12" t="n">
-        <v>7073634</v>
+        <v>7073612</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1895,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609450</v>
+        <v>122609485</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,37 +1943,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556681</v>
+        <v>556728</v>
       </c>
       <c r="R13" t="n">
-        <v>7073593</v>
+        <v>7073530</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2017,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122802580</v>
+        <v>122806389</v>
       </c>
       <c r="B14" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,39 +2065,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556617</v>
+        <v>556570</v>
       </c>
       <c r="R14" t="n">
-        <v>7073617</v>
+        <v>7073597</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2278,10 +2273,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122806389</v>
+        <v>122802567</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,34 +2289,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556570</v>
+        <v>556610</v>
       </c>
       <c r="R16" t="n">
-        <v>7073597</v>
+        <v>7073643</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122802567</v>
+        <v>122802580</v>
       </c>
       <c r="B17" t="n">
-        <v>57494</v>
+        <v>56680</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2406,16 +2406,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2426,7 +2426,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556610</v>
+        <v>556617</v>
       </c>
       <c r="R17" t="n">
-        <v>7073643</v>
+        <v>7073617</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2628,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122854282</v>
+        <v>122854275</v>
       </c>
       <c r="B19" t="n">
-        <v>90962</v>
+        <v>57631</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,34 +2644,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556672</v>
+        <v>556654</v>
       </c>
       <c r="R19" t="n">
-        <v>7073600</v>
+        <v>7073470</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2942,10 +2947,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122854278</v>
+        <v>122854280</v>
       </c>
       <c r="B22" t="n">
-        <v>79883</v>
+        <v>56680</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2954,38 +2959,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556670</v>
+        <v>556618</v>
       </c>
       <c r="R22" t="n">
-        <v>7073582</v>
+        <v>7073638</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3044,10 +3057,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122854279</v>
+        <v>122854276</v>
       </c>
       <c r="B23" t="n">
-        <v>56680</v>
+        <v>56078</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3060,21 +3073,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>206004</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3092,10 +3105,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556629</v>
+        <v>556646</v>
       </c>
       <c r="R23" t="n">
-        <v>7073587</v>
+        <v>7073479</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3154,10 +3167,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122854288</v>
+        <v>122854282</v>
       </c>
       <c r="B24" t="n">
-        <v>82553</v>
+        <v>90962</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3170,21 +3183,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,10 +3207,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556613</v>
+        <v>556672</v>
       </c>
       <c r="R24" t="n">
-        <v>7073551</v>
+        <v>7073600</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3256,10 +3269,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122854287</v>
+        <v>122854279</v>
       </c>
       <c r="B25" t="n">
-        <v>90962</v>
+        <v>56680</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,34 +3285,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556626</v>
+        <v>556629</v>
       </c>
       <c r="R25" t="n">
-        <v>7073546</v>
+        <v>7073587</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3358,10 +3379,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122854277</v>
+        <v>122854286</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3374,21 +3395,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3398,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556696</v>
+        <v>556650</v>
       </c>
       <c r="R26" t="n">
-        <v>7073607</v>
+        <v>7073472</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3460,10 +3481,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122854280</v>
+        <v>122854284</v>
       </c>
       <c r="B27" t="n">
-        <v>56680</v>
+        <v>90962</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3476,42 +3497,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556618</v>
+        <v>556746</v>
       </c>
       <c r="R27" t="n">
-        <v>7073638</v>
+        <v>7073511</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3570,10 +3583,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122854286</v>
+        <v>122854277</v>
       </c>
       <c r="B28" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3586,21 +3599,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3610,10 +3623,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556650</v>
+        <v>556696</v>
       </c>
       <c r="R28" t="n">
-        <v>7073472</v>
+        <v>7073607</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3672,10 +3685,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122854284</v>
+        <v>122854288</v>
       </c>
       <c r="B29" t="n">
-        <v>90962</v>
+        <v>82553</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3688,21 +3701,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3712,10 +3725,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556746</v>
+        <v>556613</v>
       </c>
       <c r="R29" t="n">
-        <v>7073511</v>
+        <v>7073551</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3774,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122854275</v>
+        <v>122854278</v>
       </c>
       <c r="B30" t="n">
-        <v>57631</v>
+        <v>79883</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3786,43 +3799,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556654</v>
+        <v>556670</v>
       </c>
       <c r="R30" t="n">
-        <v>7073470</v>
+        <v>7073582</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3881,10 +3889,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122854276</v>
+        <v>122854287</v>
       </c>
       <c r="B31" t="n">
-        <v>56078</v>
+        <v>90962</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3897,42 +3905,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556646</v>
+        <v>556626</v>
       </c>
       <c r="R31" t="n">
-        <v>7073479</v>
+        <v>7073546</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609323</v>
+        <v>122609342</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556565</v>
+        <v>556567</v>
       </c>
       <c r="R2" t="n">
-        <v>7073614</v>
+        <v>7073613</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609722</v>
+        <v>122609510</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556563</v>
+        <v>556718</v>
       </c>
       <c r="R3" t="n">
-        <v>7073642</v>
+        <v>7073524</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609510</v>
+        <v>122609392</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>90948</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556718</v>
+        <v>556589</v>
       </c>
       <c r="R4" t="n">
-        <v>7073524</v>
+        <v>7073595</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609342</v>
+        <v>122609367</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556567</v>
+        <v>556579</v>
       </c>
       <c r="R5" t="n">
-        <v>7073613</v>
+        <v>7073612</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609392</v>
+        <v>122609410</v>
       </c>
       <c r="B6" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556589</v>
+        <v>556627</v>
       </c>
       <c r="R6" t="n">
-        <v>7073595</v>
+        <v>7073634</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1238,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609428</v>
+        <v>122609323</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556600</v>
+        <v>556565</v>
       </c>
       <c r="R7" t="n">
-        <v>7073582</v>
+        <v>7073614</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,12 +1350,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1469,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609450</v>
+        <v>122609722</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,37 +1490,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556681</v>
+        <v>556563</v>
       </c>
       <c r="R9" t="n">
-        <v>7073593</v>
+        <v>7073642</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609394</v>
+        <v>122609485</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,34 +1607,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556621</v>
+        <v>556728</v>
       </c>
       <c r="R10" t="n">
-        <v>7073625</v>
+        <v>7073530</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1681,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122609410</v>
+        <v>122609394</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,21 +1729,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556627</v>
+        <v>556621</v>
       </c>
       <c r="R11" t="n">
-        <v>7073634</v>
+        <v>7073625</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609367</v>
+        <v>122609450</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,42 +1841,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556579</v>
+        <v>556681</v>
       </c>
       <c r="R12" t="n">
-        <v>7073612</v>
+        <v>7073593</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,12 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609485</v>
+        <v>122609428</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,39 +1953,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556728</v>
+        <v>556600</v>
       </c>
       <c r="R13" t="n">
-        <v>7073530</v>
+        <v>7073582</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,12 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,12 +2037,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122805086</v>
+        <v>122802647</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,34 +2177,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556765</v>
+        <v>556662</v>
       </c>
       <c r="R15" t="n">
-        <v>7073489</v>
+        <v>7073528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2507,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122802647</v>
+        <v>122805086</v>
       </c>
       <c r="B18" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,43 +2532,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556662</v>
+        <v>556765</v>
       </c>
       <c r="R18" t="n">
-        <v>7073528</v>
+        <v>7073489</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122854275</v>
+        <v>122854282</v>
       </c>
       <c r="B19" t="n">
-        <v>57631</v>
+        <v>90970</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,39 +2644,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556654</v>
+        <v>556672</v>
       </c>
       <c r="R19" t="n">
-        <v>7073470</v>
+        <v>7073600</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2735,7 +2730,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122854281</v>
+        <v>122854280</v>
       </c>
       <c r="B20" t="n">
         <v>56680</v>
@@ -2783,10 +2778,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556676</v>
+        <v>556618</v>
       </c>
       <c r="R20" t="n">
-        <v>7073548</v>
+        <v>7073638</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2845,10 +2840,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122854285</v>
+        <v>122854278</v>
       </c>
       <c r="B21" t="n">
-        <v>90962</v>
+        <v>79883</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2857,25 +2852,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2885,10 +2880,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556623</v>
+        <v>556670</v>
       </c>
       <c r="R21" t="n">
-        <v>7073654</v>
+        <v>7073582</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2947,10 +2942,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122854280</v>
+        <v>122854277</v>
       </c>
       <c r="B22" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2963,42 +2958,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556618</v>
+        <v>556696</v>
       </c>
       <c r="R22" t="n">
-        <v>7073638</v>
+        <v>7073607</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3057,10 +3044,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122854276</v>
+        <v>122854285</v>
       </c>
       <c r="B23" t="n">
-        <v>56078</v>
+        <v>90970</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3073,42 +3060,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556646</v>
+        <v>556623</v>
       </c>
       <c r="R23" t="n">
-        <v>7073479</v>
+        <v>7073654</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3167,10 +3146,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122854282</v>
+        <v>122854288</v>
       </c>
       <c r="B24" t="n">
-        <v>90962</v>
+        <v>82553</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3183,21 +3162,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3207,10 +3186,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556672</v>
+        <v>556613</v>
       </c>
       <c r="R24" t="n">
-        <v>7073600</v>
+        <v>7073551</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3269,7 +3248,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122854279</v>
+        <v>122854281</v>
       </c>
       <c r="B25" t="n">
         <v>56680</v>
@@ -3317,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556629</v>
+        <v>556676</v>
       </c>
       <c r="R25" t="n">
-        <v>7073587</v>
+        <v>7073548</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3379,10 +3358,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122854286</v>
+        <v>122854275</v>
       </c>
       <c r="B26" t="n">
-        <v>90962</v>
+        <v>57631</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3395,34 +3374,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556650</v>
+        <v>556654</v>
       </c>
       <c r="R26" t="n">
-        <v>7073472</v>
+        <v>7073470</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3484,7 +3468,7 @@
         <v>122854284</v>
       </c>
       <c r="B27" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3583,10 +3567,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122854277</v>
+        <v>122854286</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3599,21 +3583,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3623,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556696</v>
+        <v>556650</v>
       </c>
       <c r="R28" t="n">
-        <v>7073607</v>
+        <v>7073472</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3685,10 +3669,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122854288</v>
+        <v>122854287</v>
       </c>
       <c r="B29" t="n">
-        <v>82553</v>
+        <v>90970</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3701,21 +3685,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3725,10 +3709,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556613</v>
+        <v>556626</v>
       </c>
       <c r="R29" t="n">
-        <v>7073551</v>
+        <v>7073546</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3787,10 +3771,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122854278</v>
+        <v>122854279</v>
       </c>
       <c r="B30" t="n">
-        <v>79883</v>
+        <v>56680</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3799,38 +3783,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556670</v>
+        <v>556629</v>
       </c>
       <c r="R30" t="n">
-        <v>7073582</v>
+        <v>7073587</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3889,10 +3881,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122854287</v>
+        <v>122854276</v>
       </c>
       <c r="B31" t="n">
-        <v>90962</v>
+        <v>56078</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3905,34 +3897,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>206004</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556626</v>
+        <v>556646</v>
       </c>
       <c r="R31" t="n">
-        <v>7073546</v>
+        <v>7073479</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609342</v>
+        <v>122609323</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556567</v>
+        <v>556565</v>
       </c>
       <c r="R2" t="n">
-        <v>7073613</v>
+        <v>7073614</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609510</v>
+        <v>122609485</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556718</v>
+        <v>556728</v>
       </c>
       <c r="R3" t="n">
-        <v>7073524</v>
+        <v>7073530</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609367</v>
+        <v>122609722</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1037,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1052,7 +1057,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556579</v>
+        <v>556563</v>
       </c>
       <c r="R5" t="n">
-        <v>7073612</v>
+        <v>7073642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609410</v>
+        <v>122609548</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556627</v>
+        <v>556651</v>
       </c>
       <c r="R6" t="n">
-        <v>7073634</v>
+        <v>7073522</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1238,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609323</v>
+        <v>122609342</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556565</v>
+        <v>556567</v>
       </c>
       <c r="R7" t="n">
-        <v>7073614</v>
+        <v>7073613</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,19 +1355,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609548</v>
+        <v>122609410</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1402,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556651</v>
+        <v>556627</v>
       </c>
       <c r="R8" t="n">
-        <v>7073522</v>
+        <v>7073634</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609722</v>
+        <v>122609428</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,39 +1495,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556563</v>
+        <v>556600</v>
       </c>
       <c r="R9" t="n">
-        <v>7073642</v>
+        <v>7073582</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,22 +1579,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609485</v>
+        <v>122609394</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,39 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556728</v>
+        <v>556621</v>
       </c>
       <c r="R10" t="n">
-        <v>7073530</v>
+        <v>7073625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,12 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122609394</v>
+        <v>122609510</v>
       </c>
       <c r="B11" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,21 +1719,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556621</v>
+        <v>556718</v>
       </c>
       <c r="R11" t="n">
-        <v>7073625</v>
+        <v>7073524</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609450</v>
+        <v>122609367</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,37 +1831,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556681</v>
+        <v>556579</v>
       </c>
       <c r="R12" t="n">
-        <v>7073593</v>
+        <v>7073612</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1905,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609428</v>
+        <v>122609450</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,21 +1953,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1977,13 +1977,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556600</v>
+        <v>556681</v>
       </c>
       <c r="R13" t="n">
-        <v>7073582</v>
+        <v>7073593</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,22 +2037,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122806389</v>
+        <v>122802580</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,34 +2065,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556570</v>
+        <v>556617</v>
       </c>
       <c r="R14" t="n">
-        <v>7073597</v>
+        <v>7073617</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122802647</v>
+        <v>122802567</v>
       </c>
       <c r="B15" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,31 +2182,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2210,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556662</v>
+        <v>556610</v>
       </c>
       <c r="R15" t="n">
-        <v>7073528</v>
+        <v>7073643</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,10 +2283,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122802567</v>
+        <v>122802647</v>
       </c>
       <c r="B16" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2298,27 +2299,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2327,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556610</v>
+        <v>556662</v>
       </c>
       <c r="R16" t="n">
-        <v>7073643</v>
+        <v>7073528</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2404,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122802580</v>
+        <v>122806389</v>
       </c>
       <c r="B17" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,39 +2420,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556617</v>
+        <v>556570</v>
       </c>
       <c r="R17" t="n">
-        <v>7073617</v>
+        <v>7073597</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2628,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122854282</v>
+        <v>122854277</v>
       </c>
       <c r="B19" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,21 +2644,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556672</v>
+        <v>556696</v>
       </c>
       <c r="R19" t="n">
-        <v>7073600</v>
+        <v>7073607</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122854280</v>
+        <v>122854281</v>
       </c>
       <c r="B20" t="n">
         <v>56680</v>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556618</v>
+        <v>556676</v>
       </c>
       <c r="R20" t="n">
-        <v>7073638</v>
+        <v>7073548</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122854278</v>
+        <v>122854282</v>
       </c>
       <c r="B21" t="n">
-        <v>79883</v>
+        <v>90970</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2852,25 +2852,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556670</v>
+        <v>556672</v>
       </c>
       <c r="R21" t="n">
-        <v>7073582</v>
+        <v>7073600</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122854277</v>
+        <v>122854284</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2958,21 +2958,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556696</v>
+        <v>556746</v>
       </c>
       <c r="R22" t="n">
-        <v>7073607</v>
+        <v>7073511</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3044,7 +3044,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122854285</v>
+        <v>122854286</v>
       </c>
       <c r="B23" t="n">
         <v>90970</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556623</v>
+        <v>556650</v>
       </c>
       <c r="R23" t="n">
-        <v>7073654</v>
+        <v>7073472</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122854288</v>
+        <v>122854275</v>
       </c>
       <c r="B24" t="n">
-        <v>82553</v>
+        <v>57631</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,34 +3162,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556613</v>
+        <v>556654</v>
       </c>
       <c r="R24" t="n">
-        <v>7073551</v>
+        <v>7073470</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3248,10 +3253,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122854281</v>
+        <v>122854276</v>
       </c>
       <c r="B25" t="n">
-        <v>56680</v>
+        <v>56078</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3264,21 +3269,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>206004</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3296,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556676</v>
+        <v>556646</v>
       </c>
       <c r="R25" t="n">
-        <v>7073548</v>
+        <v>7073479</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3358,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122854275</v>
+        <v>122854287</v>
       </c>
       <c r="B26" t="n">
-        <v>57631</v>
+        <v>90970</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3374,39 +3379,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556654</v>
+        <v>556626</v>
       </c>
       <c r="R26" t="n">
-        <v>7073470</v>
+        <v>7073546</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3465,10 +3465,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122854284</v>
+        <v>122854280</v>
       </c>
       <c r="B27" t="n">
-        <v>90970</v>
+        <v>56680</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3481,34 +3481,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556746</v>
+        <v>556618</v>
       </c>
       <c r="R27" t="n">
-        <v>7073511</v>
+        <v>7073638</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3567,10 +3575,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122854286</v>
+        <v>122854279</v>
       </c>
       <c r="B28" t="n">
-        <v>90970</v>
+        <v>56680</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3583,34 +3591,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556650</v>
+        <v>556629</v>
       </c>
       <c r="R28" t="n">
-        <v>7073472</v>
+        <v>7073587</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3669,7 +3685,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122854287</v>
+        <v>122854285</v>
       </c>
       <c r="B29" t="n">
         <v>90970</v>
@@ -3709,10 +3725,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556626</v>
+        <v>556623</v>
       </c>
       <c r="R29" t="n">
-        <v>7073546</v>
+        <v>7073654</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3771,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122854279</v>
+        <v>122854288</v>
       </c>
       <c r="B30" t="n">
-        <v>56680</v>
+        <v>82553</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3787,42 +3803,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556629</v>
+        <v>556613</v>
       </c>
       <c r="R30" t="n">
-        <v>7073587</v>
+        <v>7073551</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3881,10 +3889,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122854276</v>
+        <v>122854278</v>
       </c>
       <c r="B31" t="n">
-        <v>56078</v>
+        <v>79883</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3893,46 +3901,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>206004</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556646</v>
+        <v>556670</v>
       </c>
       <c r="R31" t="n">
-        <v>7073479</v>
+        <v>7073582</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122802580</v>
+        <v>122802647</v>
       </c>
       <c r="B14" t="n">
-        <v>56680</v>
+        <v>57631</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,27 +2065,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2094,10 +2098,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556617</v>
+        <v>556662</v>
       </c>
       <c r="R14" t="n">
-        <v>7073617</v>
+        <v>7073528</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2283,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122802647</v>
+        <v>122806389</v>
       </c>
       <c r="B16" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2299,43 +2303,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556662</v>
+        <v>556570</v>
       </c>
       <c r="R16" t="n">
-        <v>7073528</v>
+        <v>7073597</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122806389</v>
+        <v>122802580</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2420,34 +2415,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556570</v>
+        <v>556617</v>
       </c>
       <c r="R17" t="n">
-        <v>7073597</v>
+        <v>7073617</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2628,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122854277</v>
+        <v>122854281</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,34 +2644,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556696</v>
+        <v>556676</v>
       </c>
       <c r="R19" t="n">
-        <v>7073607</v>
+        <v>7073548</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2730,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122854281</v>
+        <v>122854275</v>
       </c>
       <c r="B20" t="n">
-        <v>56680</v>
+        <v>57631</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2746,42 +2754,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556676</v>
+        <v>556654</v>
       </c>
       <c r="R20" t="n">
-        <v>7073548</v>
+        <v>7073470</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2840,7 +2845,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122854282</v>
+        <v>122854287</v>
       </c>
       <c r="B21" t="n">
         <v>90970</v>
@@ -2880,10 +2885,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556672</v>
+        <v>556626</v>
       </c>
       <c r="R21" t="n">
-        <v>7073600</v>
+        <v>7073546</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2942,10 +2947,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122854284</v>
+        <v>122854276</v>
       </c>
       <c r="B22" t="n">
-        <v>90970</v>
+        <v>56078</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2958,34 +2963,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>206004</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556746</v>
+        <v>556646</v>
       </c>
       <c r="R22" t="n">
-        <v>7073511</v>
+        <v>7073479</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3044,10 +3057,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122854286</v>
+        <v>122854288</v>
       </c>
       <c r="B23" t="n">
-        <v>90970</v>
+        <v>82553</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3060,21 +3073,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3084,10 +3097,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556650</v>
+        <v>556613</v>
       </c>
       <c r="R23" t="n">
-        <v>7073472</v>
+        <v>7073551</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3146,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122854275</v>
+        <v>122854282</v>
       </c>
       <c r="B24" t="n">
-        <v>57631</v>
+        <v>90970</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,39 +3175,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556654</v>
+        <v>556672</v>
       </c>
       <c r="R24" t="n">
-        <v>7073470</v>
+        <v>7073600</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3253,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122854276</v>
+        <v>122854285</v>
       </c>
       <c r="B25" t="n">
-        <v>56078</v>
+        <v>90970</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3269,42 +3277,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556646</v>
+        <v>556623</v>
       </c>
       <c r="R25" t="n">
-        <v>7073479</v>
+        <v>7073654</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122854287</v>
+        <v>122854279</v>
       </c>
       <c r="B26" t="n">
-        <v>90970</v>
+        <v>56680</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,34 +3379,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556626</v>
+        <v>556629</v>
       </c>
       <c r="R26" t="n">
-        <v>7073546</v>
+        <v>7073587</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3465,10 +3473,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122854280</v>
+        <v>122854286</v>
       </c>
       <c r="B27" t="n">
-        <v>56680</v>
+        <v>90970</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3481,42 +3489,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556618</v>
+        <v>556650</v>
       </c>
       <c r="R27" t="n">
-        <v>7073638</v>
+        <v>7073472</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3575,10 +3575,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122854279</v>
+        <v>122854278</v>
       </c>
       <c r="B28" t="n">
-        <v>56680</v>
+        <v>79883</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3587,46 +3587,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556629</v>
+        <v>556670</v>
       </c>
       <c r="R28" t="n">
-        <v>7073587</v>
+        <v>7073582</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3685,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122854285</v>
+        <v>122854277</v>
       </c>
       <c r="B29" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3701,21 +3693,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3725,10 +3717,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556623</v>
+        <v>556696</v>
       </c>
       <c r="R29" t="n">
-        <v>7073654</v>
+        <v>7073607</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3787,10 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122854288</v>
+        <v>122854284</v>
       </c>
       <c r="B30" t="n">
-        <v>82553</v>
+        <v>90970</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3803,21 +3795,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3827,10 +3819,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556613</v>
+        <v>556746</v>
       </c>
       <c r="R30" t="n">
-        <v>7073551</v>
+        <v>7073511</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3889,10 +3881,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122854278</v>
+        <v>122854280</v>
       </c>
       <c r="B31" t="n">
-        <v>79883</v>
+        <v>56680</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3901,38 +3893,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556670</v>
+        <v>556618</v>
       </c>
       <c r="R31" t="n">
-        <v>7073582</v>
+        <v>7073638</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122802647</v>
+        <v>122806389</v>
       </c>
       <c r="B14" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,43 +2065,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556662</v>
+        <v>556570</v>
       </c>
       <c r="R14" t="n">
-        <v>7073528</v>
+        <v>7073597</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2287,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122806389</v>
+        <v>122802580</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,34 +2294,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556570</v>
+        <v>556617</v>
       </c>
       <c r="R16" t="n">
-        <v>7073597</v>
+        <v>7073617</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2358,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2368,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2395,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122802580</v>
+        <v>122802647</v>
       </c>
       <c r="B17" t="n">
-        <v>56680</v>
+        <v>57631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,27 +2411,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556617</v>
+        <v>556662</v>
       </c>
       <c r="R17" t="n">
-        <v>7073617</v>
+        <v>7073528</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2628,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122854281</v>
+        <v>122854278</v>
       </c>
       <c r="B19" t="n">
-        <v>56680</v>
+        <v>79883</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2640,46 +2640,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556676</v>
+        <v>556670</v>
       </c>
       <c r="R19" t="n">
-        <v>7073548</v>
+        <v>7073582</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2738,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122854275</v>
+        <v>122854279</v>
       </c>
       <c r="B20" t="n">
-        <v>57631</v>
+        <v>56680</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2754,39 +2746,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556654</v>
+        <v>556629</v>
       </c>
       <c r="R20" t="n">
-        <v>7073470</v>
+        <v>7073587</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2947,10 +2942,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122854276</v>
+        <v>122854282</v>
       </c>
       <c r="B22" t="n">
-        <v>56078</v>
+        <v>90970</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2963,42 +2958,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556646</v>
+        <v>556672</v>
       </c>
       <c r="R22" t="n">
-        <v>7073479</v>
+        <v>7073600</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3057,10 +3044,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122854288</v>
+        <v>122854277</v>
       </c>
       <c r="B23" t="n">
-        <v>82553</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3073,21 +3060,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3097,10 +3084,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556613</v>
+        <v>556696</v>
       </c>
       <c r="R23" t="n">
-        <v>7073551</v>
+        <v>7073607</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3159,10 +3146,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122854282</v>
+        <v>122854275</v>
       </c>
       <c r="B24" t="n">
-        <v>90970</v>
+        <v>57631</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3175,34 +3162,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556672</v>
+        <v>556654</v>
       </c>
       <c r="R24" t="n">
-        <v>7073600</v>
+        <v>7073470</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3261,7 +3253,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122854285</v>
+        <v>122854284</v>
       </c>
       <c r="B25" t="n">
         <v>90970</v>
@@ -3301,10 +3293,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556623</v>
+        <v>556746</v>
       </c>
       <c r="R25" t="n">
-        <v>7073654</v>
+        <v>7073511</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3363,10 +3355,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122854279</v>
+        <v>122854276</v>
       </c>
       <c r="B26" t="n">
-        <v>56680</v>
+        <v>56078</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,21 +3371,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>206004</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3411,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556629</v>
+        <v>556646</v>
       </c>
       <c r="R26" t="n">
-        <v>7073587</v>
+        <v>7073479</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3473,10 +3465,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122854286</v>
+        <v>122854288</v>
       </c>
       <c r="B27" t="n">
-        <v>90970</v>
+        <v>82553</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3489,21 +3481,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3513,10 +3505,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556650</v>
+        <v>556613</v>
       </c>
       <c r="R27" t="n">
-        <v>7073472</v>
+        <v>7073551</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3575,10 +3567,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122854278</v>
+        <v>122854285</v>
       </c>
       <c r="B28" t="n">
-        <v>79883</v>
+        <v>90970</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3587,25 +3579,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3615,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556670</v>
+        <v>556623</v>
       </c>
       <c r="R28" t="n">
-        <v>7073582</v>
+        <v>7073654</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3677,10 +3669,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122854277</v>
+        <v>122854286</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3693,21 +3685,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3717,10 +3709,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556696</v>
+        <v>556650</v>
       </c>
       <c r="R29" t="n">
-        <v>7073607</v>
+        <v>7073472</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3779,10 +3771,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122854284</v>
+        <v>122854280</v>
       </c>
       <c r="B30" t="n">
-        <v>90970</v>
+        <v>56680</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3795,34 +3787,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556746</v>
+        <v>556618</v>
       </c>
       <c r="R30" t="n">
-        <v>7073511</v>
+        <v>7073638</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122854280</v>
+        <v>122854281</v>
       </c>
       <c r="B31" t="n">
         <v>56680</v>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556618</v>
+        <v>556676</v>
       </c>
       <c r="R31" t="n">
-        <v>7073638</v>
+        <v>7073548</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122806389</v>
+        <v>122802567</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>57497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,34 +2065,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556570</v>
+        <v>556610</v>
       </c>
       <c r="R14" t="n">
-        <v>7073597</v>
+        <v>7073643</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122802567</v>
+        <v>122805086</v>
       </c>
       <c r="B15" t="n">
-        <v>57494</v>
+        <v>79850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,39 +2182,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556610</v>
+        <v>556765</v>
       </c>
       <c r="R15" t="n">
-        <v>7073643</v>
+        <v>7073489</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122802580</v>
+        <v>122806389</v>
       </c>
       <c r="B16" t="n">
-        <v>56680</v>
+        <v>79850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,39 +2294,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556617</v>
+        <v>556570</v>
       </c>
       <c r="R16" t="n">
-        <v>7073617</v>
+        <v>7073597</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2358,7 +2353,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2368,7 +2363,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122802647</v>
+        <v>122802580</v>
       </c>
       <c r="B17" t="n">
-        <v>57631</v>
+        <v>56683</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,31 +2406,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2444,10 +2435,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556662</v>
+        <v>556617</v>
       </c>
       <c r="R17" t="n">
-        <v>7073528</v>
+        <v>7073617</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,7 +2470,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2480,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2507,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122805086</v>
+        <v>122802647</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>57634</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,34 +2523,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556765</v>
+        <v>556662</v>
       </c>
       <c r="R18" t="n">
-        <v>7073489</v>
+        <v>7073528</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122854278</v>
+        <v>122854287</v>
       </c>
       <c r="B19" t="n">
-        <v>79883</v>
+        <v>90973</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2640,25 +2640,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556670</v>
+        <v>556626</v>
       </c>
       <c r="R19" t="n">
-        <v>7073582</v>
+        <v>7073546</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2733,7 +2733,7 @@
         <v>122854279</v>
       </c>
       <c r="B20" t="n">
-        <v>56680</v>
+        <v>56683</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122854287</v>
+        <v>122854285</v>
       </c>
       <c r="B21" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556626</v>
+        <v>556623</v>
       </c>
       <c r="R21" t="n">
-        <v>7073546</v>
+        <v>7073654</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122854282</v>
+        <v>122854277</v>
       </c>
       <c r="B22" t="n">
-        <v>90970</v>
+        <v>79850</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2958,21 +2958,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556672</v>
+        <v>556696</v>
       </c>
       <c r="R22" t="n">
-        <v>7073600</v>
+        <v>7073607</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122854277</v>
+        <v>122854276</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>56081</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3060,34 +3060,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556696</v>
+        <v>556646</v>
       </c>
       <c r="R23" t="n">
-        <v>7073607</v>
+        <v>7073479</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3146,10 +3154,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122854275</v>
+        <v>122854288</v>
       </c>
       <c r="B24" t="n">
-        <v>57631</v>
+        <v>82556</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,39 +3170,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556654</v>
+        <v>556613</v>
       </c>
       <c r="R24" t="n">
-        <v>7073470</v>
+        <v>7073551</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3253,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122854284</v>
+        <v>122854278</v>
       </c>
       <c r="B25" t="n">
-        <v>90970</v>
+        <v>79886</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3265,25 +3268,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3293,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556746</v>
+        <v>556670</v>
       </c>
       <c r="R25" t="n">
-        <v>7073511</v>
+        <v>7073582</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3355,10 +3358,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122854276</v>
+        <v>122854284</v>
       </c>
       <c r="B26" t="n">
-        <v>56078</v>
+        <v>90973</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3371,42 +3374,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556646</v>
+        <v>556746</v>
       </c>
       <c r="R26" t="n">
-        <v>7073479</v>
+        <v>7073511</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3465,10 +3460,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122854288</v>
+        <v>122854286</v>
       </c>
       <c r="B27" t="n">
-        <v>82553</v>
+        <v>90973</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3481,21 +3476,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3505,10 +3500,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556613</v>
+        <v>556650</v>
       </c>
       <c r="R27" t="n">
-        <v>7073551</v>
+        <v>7073472</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3567,10 +3562,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122854285</v>
+        <v>122854282</v>
       </c>
       <c r="B28" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3607,10 +3602,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556623</v>
+        <v>556672</v>
       </c>
       <c r="R28" t="n">
-        <v>7073654</v>
+        <v>7073600</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3669,10 +3664,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122854286</v>
+        <v>122854281</v>
       </c>
       <c r="B29" t="n">
-        <v>90970</v>
+        <v>56683</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3685,34 +3680,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556650</v>
+        <v>556676</v>
       </c>
       <c r="R29" t="n">
-        <v>7073472</v>
+        <v>7073548</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3771,10 +3774,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122854280</v>
+        <v>122854275</v>
       </c>
       <c r="B30" t="n">
-        <v>56680</v>
+        <v>57634</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3787,42 +3790,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556618</v>
+        <v>556654</v>
       </c>
       <c r="R30" t="n">
-        <v>7073638</v>
+        <v>7073470</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122854281</v>
+        <v>122854280</v>
       </c>
       <c r="B31" t="n">
-        <v>56680</v>
+        <v>56683</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556676</v>
+        <v>556618</v>
       </c>
       <c r="R31" t="n">
-        <v>7073548</v>
+        <v>7073638</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122802567</v>
+        <v>122802580</v>
       </c>
       <c r="B14" t="n">
-        <v>57497</v>
+        <v>56683</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,16 +2065,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2085,7 +2085,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556610</v>
+        <v>556617</v>
       </c>
       <c r="R14" t="n">
-        <v>7073643</v>
+        <v>7073617</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122805086</v>
+        <v>122802647</v>
       </c>
       <c r="B15" t="n">
-        <v>79850</v>
+        <v>57634</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,34 +2182,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556765</v>
+        <v>556662</v>
       </c>
       <c r="R15" t="n">
-        <v>7073489</v>
+        <v>7073528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122806389</v>
+        <v>122802567</v>
       </c>
       <c r="B16" t="n">
-        <v>79850</v>
+        <v>57497</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,34 +2303,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556570</v>
+        <v>556610</v>
       </c>
       <c r="R16" t="n">
-        <v>7073597</v>
+        <v>7073643</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2363,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,10 +2404,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122802580</v>
+        <v>122805086</v>
       </c>
       <c r="B17" t="n">
-        <v>56683</v>
+        <v>79852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2406,39 +2420,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556617</v>
+        <v>556765</v>
       </c>
       <c r="R17" t="n">
-        <v>7073617</v>
+        <v>7073489</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2480,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122802647</v>
+        <v>122806389</v>
       </c>
       <c r="B18" t="n">
-        <v>57634</v>
+        <v>79852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,43 +2532,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556662</v>
+        <v>556570</v>
       </c>
       <c r="R18" t="n">
-        <v>7073528</v>
+        <v>7073597</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122854287</v>
+        <v>122854279</v>
       </c>
       <c r="B19" t="n">
-        <v>90973</v>
+        <v>56683</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,34 +2644,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556626</v>
+        <v>556629</v>
       </c>
       <c r="R19" t="n">
-        <v>7073546</v>
+        <v>7073587</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2730,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122854279</v>
+        <v>122854275</v>
       </c>
       <c r="B20" t="n">
-        <v>56683</v>
+        <v>57634</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2746,42 +2754,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556629</v>
+        <v>556654</v>
       </c>
       <c r="R20" t="n">
-        <v>7073587</v>
+        <v>7073470</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2840,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122854285</v>
+        <v>122854276</v>
       </c>
       <c r="B21" t="n">
-        <v>90973</v>
+        <v>56081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2856,34 +2861,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>206004</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556623</v>
+        <v>556646</v>
       </c>
       <c r="R21" t="n">
-        <v>7073654</v>
+        <v>7073479</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2942,10 +2955,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122854277</v>
+        <v>122854287</v>
       </c>
       <c r="B22" t="n">
-        <v>79850</v>
+        <v>90975</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2958,21 +2971,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2982,10 +2995,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556696</v>
+        <v>556626</v>
       </c>
       <c r="R22" t="n">
-        <v>7073607</v>
+        <v>7073546</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3044,10 +3057,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122854276</v>
+        <v>122854277</v>
       </c>
       <c r="B23" t="n">
-        <v>56081</v>
+        <v>79852</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3060,42 +3073,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556646</v>
+        <v>556696</v>
       </c>
       <c r="R23" t="n">
-        <v>7073479</v>
+        <v>7073607</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3154,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122854288</v>
+        <v>122854282</v>
       </c>
       <c r="B24" t="n">
-        <v>82556</v>
+        <v>90975</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3170,21 +3175,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,10 +3199,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556613</v>
+        <v>556672</v>
       </c>
       <c r="R24" t="n">
-        <v>7073551</v>
+        <v>7073600</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3256,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122854278</v>
+        <v>122854286</v>
       </c>
       <c r="B25" t="n">
-        <v>79886</v>
+        <v>90975</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3268,25 +3273,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3296,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556670</v>
+        <v>556650</v>
       </c>
       <c r="R25" t="n">
-        <v>7073582</v>
+        <v>7073472</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3358,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122854284</v>
+        <v>122854278</v>
       </c>
       <c r="B26" t="n">
-        <v>90973</v>
+        <v>79888</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3370,25 +3375,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3398,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556746</v>
+        <v>556670</v>
       </c>
       <c r="R26" t="n">
-        <v>7073511</v>
+        <v>7073582</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3460,10 +3465,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122854286</v>
+        <v>122854284</v>
       </c>
       <c r="B27" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3500,10 +3505,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556650</v>
+        <v>556746</v>
       </c>
       <c r="R27" t="n">
-        <v>7073472</v>
+        <v>7073511</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3562,10 +3567,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122854282</v>
+        <v>122854280</v>
       </c>
       <c r="B28" t="n">
-        <v>90973</v>
+        <v>56683</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3578,34 +3583,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556672</v>
+        <v>556618</v>
       </c>
       <c r="R28" t="n">
-        <v>7073600</v>
+        <v>7073638</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3664,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122854281</v>
+        <v>122854285</v>
       </c>
       <c r="B29" t="n">
-        <v>56683</v>
+        <v>90975</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3680,42 +3693,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556676</v>
+        <v>556623</v>
       </c>
       <c r="R29" t="n">
-        <v>7073548</v>
+        <v>7073654</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3774,10 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122854275</v>
+        <v>122854281</v>
       </c>
       <c r="B30" t="n">
-        <v>57634</v>
+        <v>56683</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3790,39 +3795,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556654</v>
+        <v>556676</v>
       </c>
       <c r="R30" t="n">
-        <v>7073470</v>
+        <v>7073548</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3881,10 +3889,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122854280</v>
+        <v>122854288</v>
       </c>
       <c r="B31" t="n">
-        <v>56683</v>
+        <v>82558</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3897,42 +3905,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556618</v>
+        <v>556613</v>
       </c>
       <c r="R31" t="n">
-        <v>7073638</v>
+        <v>7073551</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -3677,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122854285</v>
+        <v>122854281</v>
       </c>
       <c r="B29" t="n">
-        <v>90975</v>
+        <v>56683</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3693,34 +3693,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556623</v>
+        <v>556676</v>
       </c>
       <c r="R29" t="n">
-        <v>7073654</v>
+        <v>7073548</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3779,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122854281</v>
+        <v>122854285</v>
       </c>
       <c r="B30" t="n">
-        <v>56683</v>
+        <v>90975</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3795,42 +3803,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556676</v>
+        <v>556623</v>
       </c>
       <c r="R30" t="n">
-        <v>7073548</v>
+        <v>7073654</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122802580</v>
+        <v>122806389</v>
       </c>
       <c r="B14" t="n">
-        <v>56683</v>
+        <v>79853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,39 +2065,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556617</v>
+        <v>556570</v>
       </c>
       <c r="R14" t="n">
-        <v>7073617</v>
+        <v>7073597</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2407,7 +2402,7 @@
         <v>122805086</v>
       </c>
       <c r="B17" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2516,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122806389</v>
+        <v>122802580</v>
       </c>
       <c r="B18" t="n">
-        <v>79852</v>
+        <v>56683</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,34 +2527,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556570</v>
+        <v>556617</v>
       </c>
       <c r="R18" t="n">
-        <v>7073597</v>
+        <v>7073617</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122854279</v>
+        <v>122854276</v>
       </c>
       <c r="B19" t="n">
-        <v>56683</v>
+        <v>56081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,21 +2644,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>206004</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556629</v>
+        <v>556646</v>
       </c>
       <c r="R19" t="n">
-        <v>7073587</v>
+        <v>7073479</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122854275</v>
+        <v>122854286</v>
       </c>
       <c r="B20" t="n">
-        <v>57634</v>
+        <v>90981</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2754,39 +2754,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556654</v>
+        <v>556650</v>
       </c>
       <c r="R20" t="n">
-        <v>7073470</v>
+        <v>7073472</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2845,10 +2840,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122854276</v>
+        <v>122854282</v>
       </c>
       <c r="B21" t="n">
-        <v>56081</v>
+        <v>90981</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2861,42 +2856,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556646</v>
+        <v>556672</v>
       </c>
       <c r="R21" t="n">
-        <v>7073479</v>
+        <v>7073600</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2955,10 +2942,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122854287</v>
+        <v>122854278</v>
       </c>
       <c r="B22" t="n">
-        <v>90975</v>
+        <v>79889</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2967,25 +2954,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2995,10 +2982,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556626</v>
+        <v>556670</v>
       </c>
       <c r="R22" t="n">
-        <v>7073546</v>
+        <v>7073582</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3060,7 +3047,7 @@
         <v>122854277</v>
       </c>
       <c r="B23" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3159,10 +3146,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122854282</v>
+        <v>122854281</v>
       </c>
       <c r="B24" t="n">
-        <v>90975</v>
+        <v>56683</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3175,34 +3162,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556672</v>
+        <v>556676</v>
       </c>
       <c r="R24" t="n">
-        <v>7073600</v>
+        <v>7073548</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3261,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122854286</v>
+        <v>122854288</v>
       </c>
       <c r="B25" t="n">
-        <v>90975</v>
+        <v>82559</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3277,21 +3272,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556650</v>
+        <v>556613</v>
       </c>
       <c r="R25" t="n">
-        <v>7073472</v>
+        <v>7073551</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3363,10 +3358,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122854278</v>
+        <v>122854287</v>
       </c>
       <c r="B26" t="n">
-        <v>79888</v>
+        <v>90981</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,25 +3370,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3398,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556670</v>
+        <v>556626</v>
       </c>
       <c r="R26" t="n">
-        <v>7073582</v>
+        <v>7073546</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3465,10 +3460,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122854284</v>
+        <v>122854279</v>
       </c>
       <c r="B27" t="n">
-        <v>90975</v>
+        <v>56683</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3481,34 +3476,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556746</v>
+        <v>556629</v>
       </c>
       <c r="R27" t="n">
-        <v>7073511</v>
+        <v>7073587</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3567,10 +3570,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122854280</v>
+        <v>122854275</v>
       </c>
       <c r="B28" t="n">
-        <v>56683</v>
+        <v>57634</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3583,42 +3586,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556618</v>
+        <v>556654</v>
       </c>
       <c r="R28" t="n">
-        <v>7073638</v>
+        <v>7073470</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122854281</v>
+        <v>122854284</v>
       </c>
       <c r="B29" t="n">
-        <v>56683</v>
+        <v>90981</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3693,42 +3693,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556676</v>
+        <v>556746</v>
       </c>
       <c r="R29" t="n">
-        <v>7073548</v>
+        <v>7073511</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3787,10 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122854285</v>
+        <v>122854280</v>
       </c>
       <c r="B30" t="n">
-        <v>90975</v>
+        <v>56683</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3803,34 +3795,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556623</v>
+        <v>556618</v>
       </c>
       <c r="R30" t="n">
-        <v>7073654</v>
+        <v>7073638</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3889,10 +3889,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122854288</v>
+        <v>122854285</v>
       </c>
       <c r="B31" t="n">
-        <v>82558</v>
+        <v>90981</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3905,21 +3905,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556613</v>
+        <v>556623</v>
       </c>
       <c r="R31" t="n">
-        <v>7073551</v>
+        <v>7073654</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 58337-2024 artfynd.xlsx
+++ b/artfynd/A 58337-2024 artfynd.xlsx
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122806389</v>
+        <v>122802567</v>
       </c>
       <c r="B14" t="n">
-        <v>79853</v>
+        <v>57497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,34 +2065,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hopslåtten, Hopslåtten, Ång</t>
+          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556570</v>
+        <v>556610</v>
       </c>
       <c r="R14" t="n">
-        <v>7073597</v>
+        <v>7073643</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2282,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122802567</v>
+        <v>122805086</v>
       </c>
       <c r="B16" t="n">
-        <v>57497</v>
+        <v>79856</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2298,39 +2303,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mörtsjön, Fjällsjö s:n, Mörtsjön, Fjällsjö s:n, Ång</t>
+          <t>Hopslåtten, Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556610</v>
+        <v>556765</v>
       </c>
       <c r="R16" t="n">
-        <v>7073643</v>
+        <v>7073489</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122805086</v>
+        <v>122806389</v>
       </c>
       <c r="B17" t="n">
-        <v>79853</v>
+        <v>79856</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556765</v>
+        <v>556570</v>
       </c>
       <c r="R17" t="n">
-        <v>7073489</v>
+        <v>7073597</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2628,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122854276</v>
+        <v>122854284</v>
       </c>
       <c r="B19" t="n">
-        <v>56081</v>
+        <v>90984</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,42 +2644,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556646</v>
+        <v>556746</v>
       </c>
       <c r="R19" t="n">
-        <v>7073479</v>
+        <v>7073511</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2738,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122854286</v>
+        <v>122854285</v>
       </c>
       <c r="B20" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2778,10 +2770,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556650</v>
+        <v>556623</v>
       </c>
       <c r="R20" t="n">
-        <v>7073472</v>
+        <v>7073654</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2840,10 +2832,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122854282</v>
+        <v>122854288</v>
       </c>
       <c r="B21" t="n">
-        <v>90981</v>
+        <v>82562</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2856,21 +2848,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2880,10 +2872,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556672</v>
+        <v>556613</v>
       </c>
       <c r="R21" t="n">
-        <v>7073600</v>
+        <v>7073551</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2942,10 +2934,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122854278</v>
+        <v>122854287</v>
       </c>
       <c r="B22" t="n">
-        <v>79889</v>
+        <v>90984</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2954,25 +2946,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2982,10 +2974,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556670</v>
+        <v>556626</v>
       </c>
       <c r="R22" t="n">
-        <v>7073582</v>
+        <v>7073546</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3044,10 +3036,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122854277</v>
+        <v>122854278</v>
       </c>
       <c r="B23" t="n">
-        <v>79853</v>
+        <v>79892</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3056,25 +3048,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3084,10 +3076,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556696</v>
+        <v>556670</v>
       </c>
       <c r="R23" t="n">
-        <v>7073607</v>
+        <v>7073582</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3146,10 +3138,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122854281</v>
+        <v>122854276</v>
       </c>
       <c r="B24" t="n">
-        <v>56683</v>
+        <v>56081</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,21 +3154,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>206004</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,10 +3186,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556676</v>
+        <v>556646</v>
       </c>
       <c r="R24" t="n">
-        <v>7073548</v>
+        <v>7073479</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3256,10 +3248,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122854288</v>
+        <v>122854286</v>
       </c>
       <c r="B25" t="n">
-        <v>82559</v>
+        <v>90984</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,21 +3264,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3296,10 +3288,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556613</v>
+        <v>556650</v>
       </c>
       <c r="R25" t="n">
-        <v>7073551</v>
+        <v>7073472</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3358,10 +3350,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122854287</v>
+        <v>122854279</v>
       </c>
       <c r="B26" t="n">
-        <v>90981</v>
+        <v>56683</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3374,34 +3366,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556626</v>
+        <v>556629</v>
       </c>
       <c r="R26" t="n">
-        <v>7073546</v>
+        <v>7073587</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122854279</v>
+        <v>122854280</v>
       </c>
       <c r="B27" t="n">
         <v>56683</v>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556629</v>
+        <v>556618</v>
       </c>
       <c r="R27" t="n">
-        <v>7073587</v>
+        <v>7073638</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122854284</v>
+        <v>122854281</v>
       </c>
       <c r="B29" t="n">
-        <v>90981</v>
+        <v>56683</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3693,34 +3693,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556746</v>
+        <v>556676</v>
       </c>
       <c r="R29" t="n">
-        <v>7073511</v>
+        <v>7073548</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3779,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122854280</v>
+        <v>122854277</v>
       </c>
       <c r="B30" t="n">
-        <v>56683</v>
+        <v>79856</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3795,42 +3803,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hopslåtten, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556618</v>
+        <v>556696</v>
       </c>
       <c r="R30" t="n">
-        <v>7073638</v>
+        <v>7073607</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3889,10 +3889,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122854285</v>
+        <v>122854282</v>
       </c>
       <c r="B31" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556623</v>
+        <v>556672</v>
       </c>
       <c r="R31" t="n">
-        <v>7073654</v>
+        <v>7073600</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
